--- a/backend/data/excel/5adc9ab991cf_data.xlsx
+++ b/backend/data/excel/5adc9ab991cf_data.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>통계 ID 59</t>
+          <t>도로현황</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-21 23:33:51</t>
+          <t>2025-09-21 23:40:58</t>
         </is>
       </c>
     </row>
